--- a/File test uploads/Corp Pool Active List FileTest.xlsx
+++ b/File test uploads/Corp Pool Active List FileTest.xlsx
@@ -31,7 +31,7 @@
     <t>Designation</t>
   </si>
   <si>
-    <t>8899101</t>
+    <t>8899111</t>
   </si>
   <si>
     <t>File Test User</t>
